--- a/artfynd/A 9206-2024 artfynd.xlsx
+++ b/artfynd/A 9206-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,117 +786,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>114700440</v>
-      </c>
-      <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Uppsala (17), Upl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>637002</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6662402</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Björklinge</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>C-Upp-0979</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-09-10</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-09-10</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9206-2024 artfynd.xlsx
+++ b/artfynd/A 9206-2024 artfynd.xlsx
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103477867</v>
+        <v>131523461</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637002.3535503898</v>
+        <v>636506</v>
       </c>
       <c r="R2" t="n">
-        <v>6662401.692408024</v>
+        <v>6662475</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131523488</v>
+        <v>131523464</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636773</v>
+        <v>636373</v>
       </c>
       <c r="R3" t="n">
-        <v>6662432</v>
+        <v>6662468</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131523477</v>
+        <v>131523465</v>
       </c>
       <c r="B4" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636616</v>
+        <v>636388</v>
       </c>
       <c r="R4" t="n">
-        <v>6662445</v>
+        <v>6662462</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131523489</v>
+        <v>131523466</v>
       </c>
       <c r="B5" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636782</v>
+        <v>636381</v>
       </c>
       <c r="R5" t="n">
-        <v>6662419</v>
+        <v>6662462</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1073,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1083,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131523471</v>
+        <v>131523467</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636470</v>
+        <v>636401</v>
       </c>
       <c r="R6" t="n">
-        <v>6662440</v>
+        <v>6662471</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1190,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131523484</v>
+        <v>131523468</v>
       </c>
       <c r="B7" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636726</v>
+        <v>636434</v>
       </c>
       <c r="R7" t="n">
-        <v>6662409</v>
+        <v>6662439</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1297,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131523453</v>
+        <v>131523469</v>
       </c>
       <c r="B8" t="n">
-        <v>91862</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636745</v>
+        <v>636452</v>
       </c>
       <c r="R8" t="n">
-        <v>6662693</v>
+        <v>6662442</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1404,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131523454</v>
+        <v>131523470</v>
       </c>
       <c r="B9" t="n">
-        <v>85480</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>241</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636745</v>
+        <v>636460</v>
       </c>
       <c r="R9" t="n">
-        <v>6662693</v>
+        <v>6662443</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1511,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131523447</v>
+        <v>131523471</v>
       </c>
       <c r="B10" t="n">
-        <v>97294</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636830</v>
+        <v>636470</v>
       </c>
       <c r="R10" t="n">
-        <v>6662886</v>
+        <v>6662440</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1618,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131523464</v>
+        <v>131523473</v>
       </c>
       <c r="B11" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636373</v>
+        <v>636490</v>
       </c>
       <c r="R11" t="n">
-        <v>6662468</v>
+        <v>6662446</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131523494</v>
+        <v>131523472</v>
       </c>
       <c r="B12" t="n">
-        <v>4781</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636930</v>
+        <v>636474</v>
       </c>
       <c r="R12" t="n">
-        <v>6662363</v>
+        <v>6662449</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1822,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131523455</v>
+        <v>131523447</v>
       </c>
       <c r="B13" t="n">
-        <v>57911</v>
+        <v>97358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636726</v>
+        <v>636830</v>
       </c>
       <c r="R13" t="n">
-        <v>6662674</v>
+        <v>6662886</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1929,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131523470</v>
+        <v>131523450</v>
       </c>
       <c r="B14" t="n">
-        <v>99054</v>
+        <v>97358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636460</v>
+        <v>636815</v>
       </c>
       <c r="R14" t="n">
-        <v>6662443</v>
+        <v>6662829</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2036,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2046,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131523474</v>
+        <v>131523459</v>
       </c>
       <c r="B15" t="n">
-        <v>97919</v>
+        <v>97358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636569</v>
+        <v>636577</v>
       </c>
       <c r="R15" t="n">
-        <v>6662443</v>
+        <v>6662658</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2143,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2153,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131523498</v>
+        <v>133307001</v>
       </c>
       <c r="B16" t="n">
-        <v>99054</v>
+        <v>97435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636997</v>
+        <v>636888</v>
       </c>
       <c r="R16" t="n">
-        <v>6662399</v>
+        <v>6662492</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2245,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131523467</v>
+        <v>133307003</v>
       </c>
       <c r="B17" t="n">
-        <v>99054</v>
+        <v>97435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636401</v>
+        <v>636856</v>
       </c>
       <c r="R17" t="n">
-        <v>6662471</v>
+        <v>6662487</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,22 +2345,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131523466</v>
+        <v>131523454</v>
       </c>
       <c r="B18" t="n">
-        <v>99054</v>
+        <v>85534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>241</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636381</v>
+        <v>636745</v>
       </c>
       <c r="R18" t="n">
-        <v>6662462</v>
+        <v>6662693</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2464,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2474,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131523482</v>
+        <v>131523453</v>
       </c>
       <c r="B19" t="n">
-        <v>57911</v>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,13 +2529,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636737</v>
+        <v>636745</v>
       </c>
       <c r="R19" t="n">
-        <v>6662326</v>
+        <v>6662693</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2571,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2581,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523452</v>
+        <v>131523475</v>
       </c>
       <c r="B20" t="n">
-        <v>5179</v>
+        <v>92564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636737</v>
+        <v>636580</v>
       </c>
       <c r="R20" t="n">
-        <v>6662730</v>
+        <v>6662436</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2678,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2688,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523486</v>
+        <v>133307006</v>
       </c>
       <c r="B21" t="n">
-        <v>99054</v>
+        <v>92647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2750,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636716</v>
+        <v>636815</v>
       </c>
       <c r="R21" t="n">
-        <v>6662412</v>
+        <v>6662722</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2780,22 +2773,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,14 +2815,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523458</v>
+        <v>131523448</v>
       </c>
       <c r="B22" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2857,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636594</v>
+        <v>636827</v>
       </c>
       <c r="R22" t="n">
-        <v>6662734</v>
+        <v>6662866</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2892,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2902,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,14 +2922,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523448</v>
+        <v>131523455</v>
       </c>
       <c r="B23" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2964,13 +2957,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636827</v>
+        <v>636726</v>
       </c>
       <c r="R23" t="n">
-        <v>6662866</v>
+        <v>6662674</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2999,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3009,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,14 +3029,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131523496</v>
+        <v>131523458</v>
       </c>
       <c r="B24" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3071,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636935</v>
+        <v>636594</v>
       </c>
       <c r="R24" t="n">
-        <v>6662336</v>
+        <v>6662734</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3106,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3116,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131523475</v>
+        <v>131523460</v>
       </c>
       <c r="B25" t="n">
-        <v>92503</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636580</v>
+        <v>636590</v>
       </c>
       <c r="R25" t="n">
-        <v>6662436</v>
+        <v>6662631</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3213,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3223,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,14 +3243,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131523461</v>
+        <v>131523482</v>
       </c>
       <c r="B26" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3285,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636506</v>
+        <v>636737</v>
       </c>
       <c r="R26" t="n">
-        <v>6662475</v>
+        <v>6662326</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3320,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3330,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131523493</v>
+        <v>131523491</v>
       </c>
       <c r="B27" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3392,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636918</v>
+        <v>636818</v>
       </c>
       <c r="R27" t="n">
-        <v>6662389</v>
+        <v>6662379</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3427,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3437,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131523497</v>
+        <v>131523496</v>
       </c>
       <c r="B28" t="n">
-        <v>99054</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,13 +3492,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636970</v>
+        <v>636935</v>
       </c>
       <c r="R28" t="n">
-        <v>6662325</v>
+        <v>6662336</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3534,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3544,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131523465</v>
+        <v>131523452</v>
       </c>
       <c r="B29" t="n">
-        <v>99054</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,13 +3599,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636388</v>
+        <v>636737</v>
       </c>
       <c r="R29" t="n">
-        <v>6662462</v>
+        <v>6662730</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3641,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3651,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131523450</v>
+        <v>131523493</v>
       </c>
       <c r="B30" t="n">
-        <v>97294</v>
+        <v>4781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,13 +3706,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636815</v>
+        <v>636918</v>
       </c>
       <c r="R30" t="n">
-        <v>6662829</v>
+        <v>6662389</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3748,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3758,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131523459</v>
+        <v>131523494</v>
       </c>
       <c r="B31" t="n">
-        <v>97294</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,13 +3813,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636577</v>
+        <v>636930</v>
       </c>
       <c r="R31" t="n">
-        <v>6662658</v>
+        <v>6662363</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3855,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3865,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,48 +3885,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131523472</v>
+        <v>131523457</v>
       </c>
       <c r="B32" t="n">
-        <v>97919</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636474</v>
+        <v>636723</v>
       </c>
       <c r="R32" t="n">
-        <v>6662449</v>
+        <v>6662612</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3962,7 +3963,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3972,7 +3973,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,10 +4000,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131523468</v>
+        <v>103477867</v>
       </c>
       <c r="B33" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,19 +4029,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tolvmansmossen, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636434</v>
+        <v>637002</v>
       </c>
       <c r="R33" t="n">
-        <v>6662439</v>
+        <v>6662402</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,22 +4067,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,65 +4097,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523457</v>
+        <v>131523477</v>
       </c>
       <c r="B34" t="n">
-        <v>58073</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636723</v>
+        <v>636616</v>
       </c>
       <c r="R34" t="n">
-        <v>6662612</v>
+        <v>6662445</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,10 +4216,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131523480</v>
+        <v>131523479</v>
       </c>
       <c r="B35" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636624</v>
+        <v>636612</v>
       </c>
       <c r="R35" t="n">
-        <v>6662429</v>
+        <v>6662431</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,32 +4323,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523460</v>
+        <v>131523480</v>
       </c>
       <c r="B36" t="n">
-        <v>57911</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4363,13 +4358,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636590</v>
+        <v>636624</v>
       </c>
       <c r="R36" t="n">
-        <v>6662631</v>
+        <v>6662429</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,10 +4430,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523479</v>
+        <v>131523484</v>
       </c>
       <c r="B37" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4470,13 +4465,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636612</v>
+        <v>636726</v>
       </c>
       <c r="R37" t="n">
-        <v>6662431</v>
+        <v>6662409</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4505,7 +4500,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4515,7 +4510,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,10 +4537,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523469</v>
+        <v>131523486</v>
       </c>
       <c r="B38" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4577,10 +4572,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636452</v>
+        <v>636716</v>
       </c>
       <c r="R38" t="n">
-        <v>6662442</v>
+        <v>6662412</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4612,7 +4607,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4622,7 +4617,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4649,10 +4644,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131523473</v>
+        <v>131523488</v>
       </c>
       <c r="B39" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4684,13 +4679,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636490</v>
+        <v>636773</v>
       </c>
       <c r="R39" t="n">
-        <v>6662446</v>
+        <v>6662432</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4719,7 +4714,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4729,7 +4724,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4756,32 +4751,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523449</v>
+        <v>131523489</v>
       </c>
       <c r="B40" t="n">
-        <v>97919</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4791,13 +4786,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636813</v>
+        <v>636782</v>
       </c>
       <c r="R40" t="n">
-        <v>6662841</v>
+        <v>6662419</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4826,7 +4821,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4836,7 +4831,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,32 +4858,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523491</v>
+        <v>131523497</v>
       </c>
       <c r="B41" t="n">
-        <v>57911</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4898,13 +4893,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636818</v>
+        <v>636970</v>
       </c>
       <c r="R41" t="n">
-        <v>6662379</v>
+        <v>6662325</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4933,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4943,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4970,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133307004</v>
+        <v>131523498</v>
       </c>
       <c r="B42" t="n">
-        <v>99178</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4998,29 +4993,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636848</v>
+        <v>636997</v>
       </c>
       <c r="R42" t="n">
-        <v>6662543</v>
+        <v>6662399</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,22 +5030,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5086,45 +5072,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133307003</v>
+        <v>133307004</v>
       </c>
       <c r="B43" t="n">
-        <v>97418</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636856</v>
+        <v>636848</v>
       </c>
       <c r="R43" t="n">
-        <v>6662487</v>
+        <v>6662543</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5156,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5166,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5193,45 +5188,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133307001</v>
+        <v>133307005</v>
       </c>
       <c r="B44" t="n">
-        <v>97418</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636888</v>
+        <v>636865</v>
       </c>
       <c r="R44" t="n">
-        <v>6662492</v>
+        <v>6662566</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5263,7 +5267,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5273,7 +5277,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5300,57 +5304,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133307005</v>
+        <v>131523449</v>
       </c>
       <c r="B45" t="n">
-        <v>99178</v>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tolvmansmossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636865</v>
+        <v>636813</v>
       </c>
       <c r="R45" t="n">
-        <v>6662566</v>
+        <v>6662841</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5374,22 +5369,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5416,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133307006</v>
+        <v>131523474</v>
       </c>
       <c r="B46" t="n">
-        <v>92630</v>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5427,21 +5422,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1339</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,13 +5446,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636815</v>
+        <v>636569</v>
       </c>
       <c r="R46" t="n">
-        <v>6662722</v>
+        <v>6662443</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5481,22 +5476,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
